--- a/data/source_data/Base de Datos Proyecto NEMOS para MEGTUSALEN 18.03.26.xlsx
+++ b/data/source_data/Base de Datos Proyecto NEMOS para MEGTUSALEN 18.03.26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cristina\repos\megtusalen_validation2026\data\source_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROGRAMMING\MATLAB\MEGTUSALEN\data\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA4D0FC-ECCB-497D-B12C-F4FC02A57D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EC6EB1-520D-4DC5-8B72-5B4A073FBDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1275" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -1456,7 +1456,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:BK242"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="28.5703125" customWidth="1"/>
@@ -28233,7 +28233,7 @@
         <v>1000</v>
       </c>
       <c r="K142" s="11" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="L142" s="11" t="s">
         <v>211</v>
@@ -36378,7 +36378,7 @@
         <v>1000</v>
       </c>
       <c r="K185" s="7" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="L185" s="7" t="s">
         <v>211</v>
@@ -37514,7 +37514,7 @@
         <v>1000</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="L191" s="7" t="s">
         <v>211</v>
@@ -47214,7 +47214,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
     <col min="2" max="2" width="43.85546875" customWidth="1"/>
